--- a/config/divergent-universe-generated/templates/DivergentUniverseReview.xlsx
+++ b/config/divergent-universe-generated/templates/DivergentUniverseReview.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="T27_MechanicSourceFiles" sheetId="1" r:id="rId1"/>
-    <sheet name="T28_MechanicRules" sheetId="2" r:id="rId2"/>
+    <sheet name="T28_MechanicSourceFiles" sheetId="1" r:id="rId1"/>
+    <sheet name="T29_MechanicRules" sheetId="2" r:id="rId2"/>
     <sheet name="T01_Sources" sheetId="3" r:id="rId3"/>
     <sheet name="T02_Coverage" sheetId="4" r:id="rId4"/>
     <sheet name="T03_ResearchGaps" sheetId="5" r:id="rId5"/>
@@ -43,16 +43,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>ef1cc1687fc1f979</t>
+    <t>58351a1477631b97</t>
   </si>
   <si>
     <t>#name</t>
@@ -148,7 +148,7 @@
     <t>optional&lt;list&lt;ref&lt;DivergentUniverseMechanicRules.id&gt;&gt;&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
@@ -184,7 +184,7 @@
     <t>DivergentUniverseMechanicRules</t>
   </si>
   <si>
-    <t>0b50460bb15c3f3a</t>
+    <t>61db737043573f96</t>
   </si>
   <si>
     <t>source_file_id</t>
@@ -217,7 +217,7 @@
     <t>DivergentUniverseSources</t>
   </si>
   <si>
-    <t>45b5bcb9ce09c5b4</t>
+    <t>e09cf7b50f0dde72</t>
   </si>
   <si>
     <t>repository</t>
@@ -241,7 +241,7 @@
     <t>DivergentUniverseCoverage</t>
   </si>
   <si>
-    <t>3e4023f6704a4a3b</t>
+    <t>ded093776c9dd209</t>
   </si>
   <si>
     <t>blocking_gap_ids</t>
@@ -265,7 +265,7 @@
     <t>DivergentUniverseResearchGaps</t>
   </si>
   <si>
-    <t>31e3579bd67b4607</t>
+    <t>c19cbddc42b07ffb</t>
   </si>
   <si>
     <t>field</t>
@@ -286,7 +286,7 @@
     <t>DivergentUniverseSemanticFixtureFamilies</t>
   </si>
   <si>
-    <t>3fde11670712167e</t>
+    <t>037b0da97200cf1c</t>
   </si>
   <si>
     <t>minimum_cases</t>
@@ -298,7 +298,7 @@
     <t>DivergentUniverseReviewFixtures</t>
   </si>
   <si>
-    <t>4c7d9ad7bbb800a6</t>
+    <t>44625522a58ab03c</t>
   </si>
   <si>
     <t>family_id</t>
@@ -322,7 +322,7 @@
     <t>DivergentUniverseReconciliationReceipts</t>
   </si>
   <si>
-    <t>3bcc7fa6d46e52b1</t>
+    <t>018338fd6ad3368d</t>
   </si>
   <si>
     <t>row_locator</t>
@@ -340,7 +340,7 @@
     <t>DivergentUniverseManifest</t>
   </si>
   <si>
-    <t>0efea6e4cb517e1b</t>
+    <t>709e5840fc5816e1</t>
   </si>
   <si>
     <t>content_manifest_sha256</t>
@@ -355,7 +355,7 @@
     <t>DivergentUniversePackIndex</t>
   </si>
   <si>
-    <t>f4cd7ce332ac7d3b</t>
+    <t>3876ee1213907473</t>
   </si>
   <si>
     <t>pack_digest</t>
@@ -1172,8 +1172,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -1547,8 +1547,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -1984,8 +1984,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -2402,8 +2402,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -2812,8 +2812,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -3216,8 +3216,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -3577,8 +3577,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -4000,8 +4000,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -4403,8 +4403,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
@@ -4780,8 +4780,8 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
-      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: DivergentUniverse, Shared, OtherMode, Excluded, SharedCandidate" promptTitle="DuOwnership enum" prompt="Select a value from the dropdown." sqref="J8:J1007">
+      <formula1>"DivergentUniverse,Shared,OtherMode,Excluded,SharedCandidate"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked, Excluded" promptTitle="DuCoverageState enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
       <formula1>"Cataloged,Researched,DataReady,Blocked,Excluded"</formula1>
